--- a/plantilla_cambio_fichas.xlsx
+++ b/plantilla_cambio_fichas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Downloads\fichas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Downloads\fichas\app_conteo_fichas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E60A613-80B6-43C4-A42A-A077DFC73443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE944CE9-BAB4-48CA-AA19-F6EBC20C413F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,6 +31,7 @@
     <definedName name="Importe_3">CONFIGURACIÓN!$B$12</definedName>
     <definedName name="Importe_4">CONFIGURACIÓN!$B$13</definedName>
     <definedName name="Importe_5">CONFIGURACIÓN!$B$14</definedName>
+    <definedName name="Precio_vaso">CONFIGURACIÓN!$B$23</definedName>
     <definedName name="Texto_pie">CONFIGURACIÓN!$B$20</definedName>
     <definedName name="Texto_subtitulo">CONFIGURACIÓN!$B$18</definedName>
     <definedName name="Texto_tabla">CONFIGURACIÓN!$B$19</definedName>
@@ -68,7 +69,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="109">
+  <si>
+    <t>CAMBIOS — Nº DE FICHAS POR COMBINACIÓN</t>
+  </si>
+  <si>
+    <t>Escribe solo en las celdas AMARILLAS. Todo lo demás son fórmulas.</t>
+  </si>
+  <si>
+    <t>Cambio (€)</t>
+  </si>
+  <si>
+    <t>Combinación</t>
+  </si>
+  <si>
+    <t>Nº total de fichas</t>
+  </si>
+  <si>
+    <t>Total entregado en fichas (€)</t>
+  </si>
+  <si>
+    <t>Devolución (€)</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Sugerencia (óptima)</t>
+  </si>
+  <si>
+    <t>AUX: usa ficha 1</t>
+  </si>
+  <si>
+    <t>AUX: usa ficha 2</t>
+  </si>
+  <si>
+    <t>AUX: usa ficha 3</t>
+  </si>
+  <si>
+    <t>AUX: mínimo necesario (€)</t>
+  </si>
+  <si>
+    <t>AUX: ficha más alta (€)</t>
+  </si>
+  <si>
+    <t>AUX: ficha más baja (€)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
   <si>
     <t>CARTEL DE CAMBIO DE DINERO A FICHAS — CÓMO USAR ESTE EXCEL</t>
   </si>
@@ -193,9 +245,6 @@
     <t>Importe</t>
   </si>
   <si>
-    <t>Cambio (€)</t>
-  </si>
-  <si>
     <t>Importe 1</t>
   </si>
   <si>
@@ -244,52 +293,16 @@
     <t>¡ELIGE TU COMBINACIÓN, CAMBIA TUS EUROS POR FICHAS Y DISFRUTA!</t>
   </si>
   <si>
-    <t>CAMBIOS — Nº DE FICHAS POR COMBINACIÓN</t>
+    <t>Extra</t>
   </si>
   <si>
-    <t>Escribe solo en las celdas AMARILLAS. Todo lo demás son fórmulas.</t>
+    <t>Precio (€)</t>
   </si>
   <si>
-    <t>Combinación</t>
+    <t>Vaso</t>
   </si>
   <si>
-    <t>Nº total de fichas</t>
-  </si>
-  <si>
-    <t>Total entregado en fichas (€)</t>
-  </si>
-  <si>
-    <t>Devolución (€)</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
-    <t>Sugerencia (óptima)</t>
-  </si>
-  <si>
-    <t>AUX: usa ficha 1</t>
-  </si>
-  <si>
-    <t>AUX: usa ficha 2</t>
-  </si>
-  <si>
-    <t>AUX: usa ficha 3</t>
-  </si>
-  <si>
-    <t>AUX: mínimo necesario (€)</t>
-  </si>
-  <si>
-    <t>AUX: ficha más alta (€)</t>
-  </si>
-  <si>
-    <t>AUX: ficha más baja (€)</t>
-  </si>
-  <si>
-    <t>—</t>
+    <t>← Precio de cada vaso. La web lo suma al total.</t>
   </si>
   <si>
     <t>Cálculo de la sugerencia óptima. Para cada fila prueba a = 1..250 fichas del primer tipo y el máximo del segundo.</t>
@@ -380,6 +393,9 @@
   </si>
   <si>
     <t>pie</t>
+  </si>
+  <si>
+    <t>vaso_precio</t>
   </si>
 </sst>
 </file>
@@ -529,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -567,11 +583,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -694,10 +734,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1056,44 +1103,44 @@
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
@@ -1101,22 +1148,22 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
@@ -1124,27 +1171,27 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
@@ -1152,27 +1199,27 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
@@ -1180,12 +1227,12 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1195,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1204,97 +1251,97 @@
     <col min="5" max="5" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B5" s="7">
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B6" s="7">
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B7" s="7">
         <v>7</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B11" s="7">
         <v>20</v>
@@ -1302,7 +1349,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B12" s="7">
         <v>50</v>
@@ -1310,7 +1357,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B13" s="7">
         <v>100</v>
@@ -1318,7 +1365,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B14" s="7">
         <v>200</v>
@@ -1326,53 +1373,72 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
+        <v>64</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="46"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
+      <c r="D17" s="43"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
+      <c r="D18" s="43"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
+      <c r="D19" s="43"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
+      <c r="D20" s="43"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="7">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
@@ -1383,12 +1449,15 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="decimal" operator="greaterThan" showErrorMessage="1" errorTitle="Valor no válido" error="Debe ser un número mayor que 0." sqref="B5:B7 B10:B14" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="custom" showErrorMessage="1" errorTitle="Color no válido" error="Formato #RRGGBB, por ejemplo #F4511E." sqref="D5:D7" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>AND(LEFT(D5,1)="#",LEN(D5)=7)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" showErrorMessage="1" errorTitle="Precio no válido" error="Debe ser 0 o mayor." sqref="B23" xr:uid="{00000000-0002-0000-0100-000002000000}">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1415,9 +1484,9 @@
     <col min="20" max="21" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H1" s="12" t="str">
         <f>"Casillas en REVISAR: "&amp;COUNTIF(L5:L34,"REVISAR")</f>
@@ -1426,7 +1495,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H2" s="13" t="str">
         <f>"Casillas NO ES POSIBLE: "&amp;COUNTIF(L5:L34,"NO ES POSIBLE")</f>
@@ -1435,10 +1504,10 @@
     </row>
     <row r="4" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="str">
         <f>"Nº fichas "&amp;Valor_1&amp;" €"</f>
@@ -1465,40 +1534,40 @@
         <v>Valor 7 € (€)</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="U4" s="14" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1518,16 +1587,16 @@
         <v>9</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I5" s="20">
         <f t="shared" ref="I5:I34" si="1">IF($S5&gt;$A5,"—",SUM(C5,E5,G5))</f>
@@ -1585,10 +1654,10 @@
         <v>Solo 5 € (Calimocho)</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E6" s="29">
         <v>2</v>
@@ -1598,10 +1667,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I6" s="31">
         <f t="shared" si="1"/>
@@ -1659,16 +1728,16 @@
         <v>Solo 7 € (Cubata)</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G7" s="29">
         <v>1</v>
@@ -1747,10 +1816,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I8" s="31">
         <f t="shared" si="1"/>
@@ -1815,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G9" s="29">
         <v>1</v>
@@ -1883,10 +1952,10 @@
         <v>5 € + 7 € (Calimocho + Cubata)</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="30" t="str">
@@ -1961,16 +2030,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I11" s="20">
         <f t="shared" si="1"/>
@@ -2028,10 +2097,10 @@
         <v>Solo 5 € (Calimocho)</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E12" s="29">
         <v>4</v>
@@ -2041,10 +2110,10 @@
         <v>20</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I12" s="31">
         <f t="shared" si="1"/>
@@ -2102,16 +2171,16 @@
         <v>Solo 7 € (Cubata)</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G13" s="29">
         <v>2</v>
@@ -2190,10 +2259,10 @@
         <v>10</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I14" s="31">
         <f t="shared" si="1"/>
@@ -2258,10 +2327,10 @@
         <v>6</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G15" s="29">
         <v>2</v>
@@ -2326,10 +2395,10 @@
         <v>5 € + 7 € (Calimocho + Cubata)</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E16" s="29">
         <v>1</v>
@@ -2408,16 +2477,16 @@
         <v>48</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I17" s="20">
         <f t="shared" si="1"/>
@@ -2475,10 +2544,10 @@
         <v>Solo 5 € (Calimocho)</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E18" s="29">
         <v>10</v>
@@ -2488,10 +2557,10 @@
         <v>50</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I18" s="31">
         <f t="shared" si="1"/>
@@ -2549,16 +2618,16 @@
         <v>Solo 7 € (Cubata)</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G19" s="29">
         <v>7</v>
@@ -2637,10 +2706,10 @@
         <v>30</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I20" s="31">
         <f t="shared" si="1"/>
@@ -2705,10 +2774,10 @@
         <v>15</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G21" s="29">
         <v>5</v>
@@ -2773,10 +2842,10 @@
         <v>5 € + 7 € (Calimocho + Cubata)</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E22" s="29">
         <v>3</v>
@@ -2855,16 +2924,16 @@
         <v>99</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="1"/>
@@ -2922,10 +2991,10 @@
         <v>Solo 5 € (Calimocho)</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E24" s="29">
         <v>20</v>
@@ -2935,10 +3004,10 @@
         <v>100</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I24" s="31">
         <f t="shared" si="1"/>
@@ -2996,16 +3065,16 @@
         <v>Solo 7 € (Cubata)</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G25" s="29">
         <v>14</v>
@@ -3084,10 +3153,10 @@
         <v>75</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I26" s="31">
         <f t="shared" si="1"/>
@@ -3152,10 +3221,10 @@
         <v>30</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G27" s="29">
         <v>10</v>
@@ -3220,10 +3289,10 @@
         <v>5 € + 7 € (Calimocho + Cubata)</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E28" s="29">
         <v>13</v>
@@ -3302,16 +3371,16 @@
         <v>198</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I29" s="20">
         <f t="shared" si="1"/>
@@ -3369,10 +3438,10 @@
         <v>Solo 5 € (Calimocho)</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E30" s="29">
         <v>40</v>
@@ -3382,10 +3451,10 @@
         <v>200</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I30" s="31">
         <f t="shared" si="1"/>
@@ -3443,16 +3512,16 @@
         <v>Solo 7 € (Cubata)</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G31" s="29">
         <v>28</v>
@@ -3531,10 +3600,10 @@
         <v>150</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I32" s="31">
         <f t="shared" si="1"/>
@@ -3599,10 +3668,10 @@
         <v>45</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="G33" s="29">
         <v>22</v>
@@ -3667,10 +3736,10 @@
         <v>5 € + 7 € (Calimocho + Cubata)</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E34" s="29">
         <v>19</v>
@@ -3768,38 +3837,38 @@
   <sheetData>
     <row r="1" spans="1:259" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:259" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:259" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -35594,51 +35663,51 @@
     <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="K4" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B5" s="27">
         <f>Valor_1</f>
@@ -35678,7 +35747,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B6" s="27" t="str">
         <f>Bebida_1</f>
@@ -35718,7 +35787,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B7" s="27" t="str">
         <f>Color_1</f>
@@ -35758,7 +35827,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" s="27">
         <f>Valor_2</f>
@@ -35798,7 +35867,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B9" s="27" t="str">
         <f>Bebida_2</f>
@@ -35836,9 +35905,9 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B10" s="27" t="str">
         <f>Color_2</f>
@@ -35878,7 +35947,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B11" s="27">
         <f>Valor_3</f>
@@ -35918,7 +35987,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B12" s="27" t="str">
         <f>Bebida_3</f>
@@ -35958,7 +36027,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B13" s="27" t="str">
         <f>Color_3</f>
@@ -35998,7 +36067,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B14" s="27" t="str">
         <f>Texto_titulo</f>
@@ -36038,7 +36107,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B15" s="27" t="str">
         <f>Texto_subtitulo</f>
@@ -36078,7 +36147,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B16" s="27" t="str">
         <f>Texto_tabla</f>
@@ -36116,9 +36185,9 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B17" s="27" t="str">
         <f>Texto_pie</f>
@@ -36157,6 +36226,13 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="27">
+        <f>Precio_vaso</f>
+        <v>1</v>
+      </c>
       <c r="D18" s="30">
         <f>CAMBIOS!A18</f>
         <v>50</v>
